--- a/sources/baek_step6b.xlsx
+++ b/sources/baek_step6b.xlsx
@@ -421,16 +421,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="25" customWidth="1" min="9" max="9"/>
     <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -2537,12 +2537,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>– 3 [~f_~b]</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>– High Kick [FLA]</t>
+          <t>– High Kick</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2790,12 +2795,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>– 3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>– 3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>– Black Widow [FLA]</t>
+          <t>– Black Widow</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3569,12 +3579,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Black Widow [FLA]</t>
+          <t>Black Widow</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3822,12 +3837,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>WS+3,4&lt;4,3 [~f_~b]</t>
+          <t>WS+3,4&lt;4,3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Eliminator [FLA]</t>
+          <t>Eliminator</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4323,12 +4343,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>– 3,3,4&lt;4&lt;3 [~f_~b]</t>
+          <t>– 3,3,4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>– Black Widow [FLA]</t>
+          <t>– Black Widow</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>(~f)FLA; (~b)FLA</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4715,17 +4740,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>3+4 [f_b]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>uf+3+4 [f_b]</t>
+          <t>uf+3+4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5040,12 +5070,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>f+4&lt;3 [f_b]</t>
+          <t>f+4&lt;3</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Heel Knife [FLA]</t>
+          <t>Heel Knife</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5169,12 +5204,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>WS+4&lt;4&lt;3 [f_b]</t>
+          <t>WS+4&lt;4&lt;3</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5298,12 +5338,17 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>df+4~4&lt;3 [f_b]</t>
+          <t>df+4~4&lt;3</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Albatross [FLA]</t>
+          <t>Albatross</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5427,17 +5472,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FC+4,3,3&lt;3 [f_b]</t>
+          <t>FC+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>d+4,3,3&lt;3 [f_b]</t>
+          <t>d+4,3,3&lt;3</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Baek Rush [FLA]</t>
+          <t>Baek Rush</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5603,12 +5653,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>b+1+2 [~B]</t>
+          <t>b+1+2</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>High &amp; Mid Punch Parry [FLA]</t>
+          <t>High &amp; Mid Punch Parry</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>(~B)FLA</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6109,12 +6164,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3,4,4,3 [f_b]</t>
+          <t>3,4,4,3</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Flamingo Eliminator [FLA]</t>
+          <t>Flamingo Eliminator</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6332,12 +6392,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>N+4 [f_b]</t>
+          <t>N+4</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Flashing Halbred [FLA]</t>
+          <t>Flashing Halbred</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>(~F)FLA; (~B)FLA</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6493,7 +6558,7 @@
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="O109" t="inlineStr">
@@ -6660,7 +6725,7 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
@@ -6876,7 +6941,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>hhhlmmmlm[!]</t>
+          <t>hhhlmmmlm!</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">

--- a/sources/baek_step6b.xlsx
+++ b/sources/baek_step6b.xlsx
@@ -837,6 +837,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>a8cff31e-973f-4967-a9af-aeb862702e75</t>
@@ -884,6 +889,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>23f4e603-2800-445d-a580-a5449bb4e6db</t>
@@ -929,6 +939,11 @@
       <c r="M10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>c1e72722-088e-4713-997a-36ef818af837</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -6912,6 +6927,11 @@
           <t>hhlmmmhmlm</t>
         </is>
       </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
+        </is>
+      </c>
       <c r="R118" t="inlineStr">
         <is>
           <t>b9450184-4f85-4745-a77d-d804cc3878f8</t>
@@ -6942,6 +6962,11 @@
       <c r="K119" t="inlineStr">
         <is>
           <t>hhhlmmmlm!</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>26c9b6a0-30d4-4ef8-b80e-04220b821fe5</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
